--- a/data/trans_dic/P13A_1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_2023-Habitat-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,01; 100,0</t>
+          <t>79,05; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,14; 100,0</t>
+          <t>83,24; 100,0</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,67; 100,0</t>
+          <t>91,18; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,76; 100,0</t>
+          <t>93,65; 100,0</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,39; 100,0</t>
+          <t>87,0; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,64; 100,0</t>
+          <t>88,92; 100,0</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,6; 97,38</t>
+          <t>74,1; 97,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,24; 97,86</t>
+          <t>75,87; 97,6</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,46; 97,41</t>
+          <t>88,96; 97,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,82; 97,98</t>
+          <t>90,62; 97,63</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>33860</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20112; 25454</t>
+          <t>21166; 26776</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28040; 33725</t>
+          <t>29486; 35422</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>64003</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41424; 45187</t>
+          <t>45796; 50227</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56212; 59955</t>
+          <t>61010; 65150</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39315</t>
+          <t>46360</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28402; 31772</t>
+          <t>32614; 37488</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36711; 40062</t>
+          <t>42577; 47880</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>50767</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36373; 48126</t>
+          <t>36955; 48462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41193; 54299</t>
+          <t>42352; 54485</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134306; 147895</t>
+          <t>146218; 159931</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171861; 185399</t>
+          <t>185120; 199435</t>
         </is>
       </c>
     </row>
